--- a/out/Attention-mamba2_repeat_2_000006.xlsx
+++ b/out/Attention-mamba2_repeat_2_000006.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.931760215741336</v>
+        <v>2.648249220197788</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.931760215741336</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.931760215741336</v>
+        <v>-0.3648012947504815</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.931760215741336</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.931760215741336</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.931760215741336</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.931760215741336</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.931760215741336</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.931760215741336</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.931760215741336</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.931760215741336</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.931760215741336</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.931760215741336</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.931760215741336</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-1.931760215741336</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.931760215741336</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-1.931760215741336</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.931760215741336</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.931760215741336</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-1.931760215741336</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.931760215741336</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.931760215741336</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.931760215741336</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-1.931760215741336</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.931760215741336</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-1.931760215741336</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.931760215741336</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-1.931760215741336</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-1.931760215741336</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-1.931760215741336</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.931760215741336</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.931760215741336</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.931760215741336</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-1.931760215741336</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-1.931760215741336</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-1.931760215741336</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-1.931760215741336</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-1.931760215741336</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-1.931760215741336</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>-1.931760215741336</v>
+        <v>3.248249220197788</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34327,14 +34327,14 @@
       </c>
       <c r="IZ42" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>-1.931760215741336</v>
+        <v>3.248249220197788</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35122,14 +35122,14 @@
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>-1.931760215741336</v>
+        <v>3.248249220197788</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35917,17 +35917,17 @@
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA44" t="n">
         <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-1.931760215741336</v>
+        <v>-0.3648012947504815</v>
       </c>
       <c r="JC44" t="n">
-        <v>0</v>
+        <v>-5.812476011051331e-05</v>
       </c>
     </row>
     <row r="45">
@@ -36708,21 +36708,21 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0</v>
+        <v>0.07481088350101807</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA45" t="n">
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-1.931760215741336</v>
+        <v>-0.3648012947504815</v>
       </c>
       <c r="JC45" t="n">
-        <v>0</v>
+        <v>0.1497637670641986</v>
       </c>
     </row>
     <row r="46">
@@ -37503,21 +37503,21 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0</v>
+        <v>-0.01727700517808899</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>StopLoss</t>
         </is>
       </c>
       <c r="JA46" t="n">
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.931760215741336</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC46" t="n">
-        <v>0</v>
+        <v>0.05747575356281851</v>
       </c>
     </row>
     <row r="47">
@@ -38302,17 +38302,17 @@
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA47" t="n">
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.931760215741336</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC47" t="n">
-        <v>0</v>
+        <v>0.05747575356281851</v>
       </c>
     </row>
     <row r="48">
@@ -39097,17 +39097,17 @@
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA48" t="n">
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.931760215741336</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC48" t="n">
-        <v>0</v>
+        <v>0.05745598579857708</v>
       </c>
     </row>
     <row r="49">
@@ -39888,21 +39888,21 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0</v>
+        <v>0.0607308469105507</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA49" t="n">
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.931760215741336</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC49" t="n">
-        <v>0</v>
+        <v>0.1790386089303726</v>
       </c>
     </row>
     <row r="50">
@@ -40683,21 +40683,21 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0</v>
+        <v>0.01162016326218521</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA50" t="n">
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.931760215741336</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC50" t="n">
-        <v>0</v>
+        <v>0.1414594637583599</v>
       </c>
     </row>
     <row r="51">
@@ -41478,21 +41478,21 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0</v>
+        <v>0.02035360045113625</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA51" t="n">
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.931760215741336</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC51" t="n">
-        <v>0</v>
+        <v>0.170552632992587</v>
       </c>
     </row>
     <row r="52">
@@ -42273,21 +42273,21 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0</v>
+        <v>0.01114546361860735</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA52" t="n">
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.931760215741336</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC52" t="n">
-        <v>0</v>
+        <v>0.1724733663858718</v>
       </c>
     </row>
     <row r="53">
@@ -43068,21 +43068,21 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0</v>
+        <v>0.004600565325946042</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>1.501156825476262</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.0002002309455162613</v>
+        <v>0.1705192084224697</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.2348532448241971</v>
+        <v>0.005732862279140122</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.331760215741336</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.4701604531224964</v>
+        <v>0.1773849858380402</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.1575410585012543</v>
+        <v>0.003449915309386803</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>1.501156825476262</v>
+        <v>3.248249220197788</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.5501229848337783</v>
+        <v>0.1785488402471298</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.1403261406329832</v>
+        <v>0.002621640260101849</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.331760215741336</v>
+        <v>-0.3648012947504815</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.6731323587503312</v>
+        <v>0.1803410247823449</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.05978859537667826</v>
+        <v>0.001156772499925905</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>1.501156825476262</v>
+        <v>3.248249220197788</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.6522248212284448</v>
+        <v>0.1800310767931424</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.05323580277801146</v>
+        <v>0.0009156073118376191</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.501156825476262</v>
+        <v>3.248249220197788</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.6988813181523746</v>
+        <v>0.1807077080886841</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.02635854469684114</v>
+        <v>0.0004527708881848236</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.501156825476262</v>
+        <v>-0.3648012947504815</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.6983128077869045</v>
+        <v>0.1806945380144655</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.01572961315470562</v>
+        <v>0.0002597372678522882</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>1.501156825476262</v>
+        <v>-0.3648012947504815</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.7033932303750317</v>
+        <v>0.1807639108899508</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.007863896966474569</v>
+        <v>0.0001288232342989589</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>1.501156825476262</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.7033768966635677</v>
+        <v>0.1807587442709904</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.00387415082901298</v>
+        <v>6.111690773477915e-05</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>1.501156825476262</v>
+        <v>2.648249220197788</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.7032580516182163</v>
+        <v>0.1807520705878837</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.002296645023843939</v>
+        <v>3.17141805569301e-05</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>1</v>
       </c>
       <c r="JB63" t="n">
-        <v>1.501156825476262</v>
+        <v>3.248249220197788</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.7039752893440894</v>
+        <v>0.1807576869822952</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.0007135005903250154</v>
+        <v>8.391820683831448e-06</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>1</v>
       </c>
       <c r="JB64" t="n">
-        <v>1.501156825476262</v>
+        <v>3.248249220197788</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.7031024015478375</v>
+        <v>0.1807393859983794</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.0003578780163979938</v>
+        <v>1.73737344181313e-06</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.501156825476262</v>
+        <v>3.248249220197788</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.7031022721818614</v>
+        <v>0.1807344605489003</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.0001960786965170683</v>
+        <v>-2.553803869891494e-06</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>0.9011568254762616</v>
+        <v>3.248249220197788</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.7031362982943113</v>
+        <v>0.1807300594202953</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>9.181457978441713e-05</v>
+        <v>-2.629819553036738e-06</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>0.9011568254762616</v>
+        <v>-0.3648012947504815</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.7031236940542366</v>
+        <v>0.1807249042317225</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>5.535587318484808e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.9011568254762616</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.7031450508497122</v>
+        <v>0.1807254438996226</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>2.119747900227306e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>0.9011568254762616</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.7031317095831053</v>
+        <v>0.1807251117962995</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>1.037920999549386e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>0.9011568254762616</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.7031316344572404</v>
+        <v>0.1807254923313572</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>3.373746146054129e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57389,10 +57389,10 @@
         <v>1</v>
       </c>
       <c r="JB71" t="n">
-        <v>0.9011568254762616</v>
+        <v>2.648249220197788</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.7031282208417191</v>
+        <v>0.1807257206523919</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>7.621708635915141e-07</v>
+        <v>0</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>0.9011568254762616</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.7031235724959429</v>
+        <v>0.1807258105970418</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>-2.975818632750635e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58979,10 +58979,10 @@
         <v>1</v>
       </c>
       <c r="JB73" t="n">
-        <v>0.9011568254762616</v>
+        <v>3.248249220197788</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.7031168535961052</v>
+        <v>0.180724952663457</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>0.9011568254762616</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.70311708191714</v>
+        <v>0.1807251809844917</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>0.9011568254762616</v>
+        <v>-0.3648012947504815</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.7031162862529282</v>
+        <v>0.18072438532028</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>0.9011568254762616</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.7031163485223013</v>
+        <v>0.1807244475896531</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>0.9011568254762616</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.7031163761975782</v>
+        <v>0.1807244752649299</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>0.9011568254762616</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.7031165284116014</v>
+        <v>0.1807246274789532</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>0.9011568254762616</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.7031161824706397</v>
+        <v>0.1807242815379915</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>0.9011568254762616</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.7031162585776514</v>
+        <v>0.1807243576450031</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.9011568254762616</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.7031164246293129</v>
+        <v>0.1807245236966647</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.9011568254762616</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.703116784407913</v>
+        <v>0.1807248834752648</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.9011568254762616</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.7031168051643707</v>
+        <v>0.1807249042317225</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.9011568254762616</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.7031169089466592</v>
+        <v>0.180725008014011</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.9011568254762616</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.7031171372676939</v>
+        <v>0.1807252363350457</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>1</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.9011568254762616</v>
+        <v>3.248249220197788</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.7031170127289477</v>
+        <v>0.1807251117962995</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.9011568254762616</v>
+        <v>3.248249220197788</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.7031170404042245</v>
+        <v>0.1807251394715763</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.9011568254762616</v>
+        <v>3.248249220197788</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.7031170957547784</v>
+        <v>0.1807251948221303</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.9011568254762616</v>
+        <v>-0.3648012947504815</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.7031173586699092</v>
+        <v>0.180725457737261</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.9011568254762616</v>
+        <v>-0.3648012947504815</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.7031172756440783</v>
+        <v>0.1807253747114302</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>1</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.9011568254762616</v>
+        <v>2.648249220197788</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.7031170680795016</v>
+        <v>0.1807251671468534</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.9011568254762616</v>
+        <v>3.248249220197788</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.70311708191714</v>
+        <v>0.1807251809844917</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>1</v>
       </c>
       <c r="JB93" t="n">
-        <v>0.9011568254762616</v>
+        <v>3.248249220197788</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.7031172202935246</v>
+        <v>0.1807253193608765</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.9011568254762616</v>
+        <v>3.248249220197788</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.7031169366219361</v>
+        <v>0.1807250356892878</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.9011568254762616</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.7031167636514553</v>
+        <v>0.1807248627188071</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>0.9011568254762616</v>
+        <v>2.648249220197788</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.7031166598691668</v>
+        <v>0.1807247589365186</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>1</v>
       </c>
       <c r="JB97" t="n">
-        <v>0.9011568254762616</v>
+        <v>2.648249220197788</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.7031168051643707</v>
+        <v>0.1807249042317225</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>0.9011568254762616</v>
+        <v>-0.3648012947504815</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.7031170473230439</v>
+        <v>0.1807251463903957</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.9011568254762616</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.703116874352563</v>
+        <v>0.1807249734199147</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.9011568254762616</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.7031165768433359</v>
+        <v>0.1807246759106878</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.9011568254762616</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.7031165630056975</v>
+        <v>0.1807246620730492</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.9011568254762616</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.7031161963082783</v>
+        <v>0.18072429537563</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.9011568254762616</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.7031161963082783</v>
+        <v>0.18072429537563</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.9011568254762616</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.7031161340389052</v>
+        <v>0.1807242331062569</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>0.9011568254762616</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.7031160302566166</v>
+        <v>0.1807241293239684</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>0.9011568254762616</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.7031158572861359</v>
+        <v>0.1807239563534877</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>0.9011568254762616</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.7031159057178704</v>
+        <v>0.1807240047852222</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>0.9011568254762616</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.7031155459392704</v>
+        <v>0.1807236450066222</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>0.9011568254762616</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.703115504426355</v>
+        <v>0.1807236034937068</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>0.9011568254762616</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.7031155597769088</v>
+        <v>0.1807236588442605</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>0.9011568254762616</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.7031156151274627</v>
+        <v>0.1807237141948144</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>0.9011568254762616</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.703115656640378</v>
+        <v>0.1807237557077298</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>0.9011568254762616</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.7031153868064279</v>
+        <v>0.1807234858737798</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.9011568254762616</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.703115442156982</v>
+        <v>0.1807235412243337</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.9011568254762616</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.7031155874521858</v>
+        <v>0.1807236865195376</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.9011568254762616</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.7031155528580896</v>
+        <v>0.1807236519254413</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.9011568254762616</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.703115539020451</v>
+        <v>0.1807236380878028</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.9011568254762616</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.7031156289651012</v>
+        <v>0.180723728032453</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.9011568254762616</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.7031159472307859</v>
+        <v>0.1807240462981376</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.9011568254762616</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.7031157673414857</v>
+        <v>0.1807238664088375</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>0.9011568254762616</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.7031158088544011</v>
+        <v>0.1807239079217529</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>0.9011568254762616</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.7031156220462819</v>
+        <v>0.1807237211136336</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>0.9011568254762616</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.7031156912344743</v>
+        <v>0.1807237903018261</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.9011568254762616</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.7031154905887165</v>
+        <v>0.1807235896560682</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>0.9011568254762616</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.7031155321016319</v>
+        <v>0.1807236311689837</v>
       </c>
     </row>
     <row r="126">
@@ -101103,7 +101103,7 @@
         <v>0</v>
       </c>
       <c r="IY126" t="n">
-        <v>-4.268085246219792e-06</v>
+        <v>-3.873712549958921e-06</v>
       </c>
       <c r="IZ126" t="inlineStr">
         <is>
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>0.9011568254762616</v>
+        <v>-0.9648012947504814</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.7031155597769088</v>
+        <v>0.1807236588442605</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-mamba2_repeat_2_000006.xlsx
+++ b/out/Attention-mamba2_repeat_2_000006.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.931760215741336</v>
+        <v>-1.158921290794059</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.931760215741336</v>
+        <v>-1.158921290794059</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.931760215741336</v>
+        <v>-1.158921290794059</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.931760215741336</v>
+        <v>-1.158921290794059</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.931760215741336</v>
+        <v>-1.158921290794059</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.931760215741336</v>
+        <v>-1.158921290794059</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.931760215741336</v>
+        <v>-1.158921290794059</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.931760215741336</v>
+        <v>-1.158921290794059</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.931760215741336</v>
+        <v>-1.158921290794059</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.931760215741336</v>
+        <v>-1.158921290794059</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.931760215741336</v>
+        <v>-1.158921290794059</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.931760215741336</v>
+        <v>-1.158921290794059</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.931760215741336</v>
+        <v>-1.158921290794059</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.931760215741336</v>
+        <v>-1.158921290794059</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-1.931760215741336</v>
+        <v>-1.158921290794059</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.931760215741336</v>
+        <v>-1.158921290794059</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-1.931760215741336</v>
+        <v>-1.158921290794059</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.931760215741336</v>
+        <v>-1.158921290794059</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.931760215741336</v>
+        <v>-1.158921290794059</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-1.931760215741336</v>
+        <v>-1.158921290794059</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.931760215741336</v>
+        <v>-1.158921290794059</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.931760215741336</v>
+        <v>-1.158921290794059</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.931760215741336</v>
+        <v>-1.158921290794059</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>-1.931760215741336</v>
+        <v>-1.158921290794059</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.931760215741336</v>
+        <v>-1.158921290794059</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-1.931760215741336</v>
+        <v>-1.158921290794059</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.931760215741336</v>
+        <v>-1.158921290794059</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-1.931760215741336</v>
+        <v>-1.158921290794059</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-1.931760215741336</v>
+        <v>-1.158921290794059</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-1.931760215741336</v>
+        <v>-1.158921290794059</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.931760215741336</v>
+        <v>-1.158921290794059</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.931760215741336</v>
+        <v>-1.158921290794059</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.931760215741336</v>
+        <v>-1.158921290794059</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-1.931760215741336</v>
+        <v>-1.158921290794059</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-1.931760215741336</v>
+        <v>-1.158921290794059</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-1.931760215741336</v>
+        <v>-1.158921290794059</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-1.931760215741336</v>
+        <v>-1.158921290794059</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-1.931760215741336</v>
+        <v>-1.158921290794059</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-1.931760215741336</v>
+        <v>-1.158921290794059</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-1.931760215741336</v>
+        <v>-1.158921290794059</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-1.931760215741336</v>
+        <v>-1.158921290794059</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-1.931760215741336</v>
+        <v>-1.158921290794059</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-1.931760215741336</v>
+        <v>-1.158921290794059</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36719,7 +36719,7 @@
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-1.931760215741336</v>
+        <v>-1.158921290794059</v>
       </c>
       <c r="JC45" t="n">
         <v>0</v>
@@ -37514,7 +37514,7 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.931760215741336</v>
+        <v>-1.158921290794059</v>
       </c>
       <c r="JC46" t="n">
         <v>0</v>
@@ -38309,7 +38309,7 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.931760215741336</v>
+        <v>-1.158921290794059</v>
       </c>
       <c r="JC47" t="n">
         <v>0</v>
@@ -39097,17 +39097,17 @@
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA48" t="n">
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.931760215741336</v>
+        <v>-1.158921290794059</v>
       </c>
       <c r="JC48" t="n">
-        <v>0</v>
+        <v>-5.933721306733787e-06</v>
       </c>
     </row>
     <row r="49">
@@ -39888,21 +39888,21 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0</v>
+        <v>0.007169178160520064</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA49" t="n">
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.931760215741336</v>
+        <v>-1.158921290794059</v>
       </c>
       <c r="JC49" t="n">
-        <v>0</v>
+        <v>0.01434917160715582</v>
       </c>
     </row>
     <row r="50">
@@ -40683,21 +40683,21 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0</v>
+        <v>0.001367976758648252</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA50" t="n">
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.931760215741336</v>
+        <v>-1.158921290794059</v>
       </c>
       <c r="JC50" t="n">
-        <v>0</v>
+        <v>0.009907249804488849</v>
       </c>
     </row>
     <row r="51">
@@ -41478,21 +41478,21 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0</v>
+        <v>0.002399242476805734</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA51" t="n">
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.931760215741336</v>
+        <v>-1.158921290794059</v>
       </c>
       <c r="JC51" t="n">
-        <v>0</v>
+        <v>0.01333873167907086</v>
       </c>
     </row>
     <row r="52">
@@ -42273,21 +42273,21 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0</v>
+        <v>0.001311642320319503</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA52" t="n">
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.931760215741336</v>
+        <v>-0.3113973956586084</v>
       </c>
       <c r="JC52" t="n">
-        <v>0</v>
+        <v>0.01356115812523325</v>
       </c>
     </row>
     <row r="53">
@@ -43068,21 +43068,21 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0</v>
+        <v>0.000538800078243116</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
-          <t>Buy</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA53" t="n">
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>1.501156825476262</v>
+        <v>-0.3113973956586084</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.0002002309455162613</v>
+        <v>0.01332592913946242</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.2348532448241971</v>
+        <v>0.0006729861208765089</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-1.331760215741336</v>
+        <v>0.3361264994768428</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.4701604531224964</v>
+        <v>0.01413278057485225</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.1575410585012543</v>
+        <v>0.0004026421962169791</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>1.501156825476262</v>
+        <v>-0.3113973956586084</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.5501229848337783</v>
+        <v>0.01426589324904222</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.1403261406329832</v>
+        <v>0.0003058131087535019</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.331760215741336</v>
+        <v>0.3361264994768428</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.6731323587503312</v>
+        <v>0.01447355598816136</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.05978859537667826</v>
+        <v>0.0001316791176383418</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>1.501156825476262</v>
+        <v>0.3361264994768428</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.6522248212284448</v>
+        <v>0.01443247218956053</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.05323580277801146</v>
+        <v>0.0001034551079699113</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.501156825476262</v>
+        <v>0.9836503946122938</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.6988813181523746</v>
+        <v>0.01450859796156152</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.02635854469684114</v>
+        <v>5.003256579271103e-05</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.501156825476262</v>
+        <v>0.9836503946122938</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.6983128077869045</v>
+        <v>0.01450261576684681</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.01572961315470562</v>
+        <v>2.700120820192495e-05</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>1.501156825476262</v>
+        <v>0.9836503946122938</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.7033932303750317</v>
+        <v>0.01450655655054632</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.007863896966474569</v>
+        <v>9.546003728147707e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>1.501156825476262</v>
+        <v>0.9836503946122938</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.7033768966635677</v>
+        <v>0.01450153843978979</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.00387415082901298</v>
+        <v>3.623944487145107e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>1.501156825476262</v>
+        <v>0.9836503946122938</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.7032580516182163</v>
+        <v>0.01449632013329759</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.002296645023843939</v>
+        <v>-1.662347222097263e-06</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>1</v>
       </c>
       <c r="JB63" t="n">
-        <v>1.501156825476262</v>
+        <v>0.9836503946122938</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.7039752893440894</v>
+        <v>0.01449270667905186</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.0007135005903250154</v>
+        <v>-2.768029886028092e-06</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>1</v>
       </c>
       <c r="JB64" t="n">
-        <v>1.501156825476262</v>
+        <v>0.9836503946122938</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.7031024015478375</v>
+        <v>0.0144854898483993</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.0003578780163979938</v>
+        <v>0</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.501156825476262</v>
+        <v>0.9836503946122938</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.7031022721818614</v>
+        <v>0.01448550368603773</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.0001960786965170683</v>
+        <v>0</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>0.9011568254762616</v>
+        <v>0.9836503946122938</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.7031362982943113</v>
+        <v>0.01448570433179545</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>9.181457978441713e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>0.9011568254762616</v>
+        <v>0.7836503946122937</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.7031236940542366</v>
+        <v>0.01448562822478393</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>5.535587318484808e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>1</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.9011568254762616</v>
+        <v>0.7836503946122937</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.7031450508497122</v>
+        <v>0.01448616789268411</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>2.119747900227306e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>1</v>
       </c>
       <c r="JB69" t="n">
-        <v>0.9011568254762616</v>
+        <v>0.7836503946122937</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.7031317095831053</v>
+        <v>0.01448583578936092</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>1.037920999549386e-05</v>
+        <v>0</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>1</v>
       </c>
       <c r="JB70" t="n">
-        <v>0.9011568254762616</v>
+        <v>0.7836503946122937</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.7031316344572404</v>
+        <v>0.01448621632441867</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>3.373746146054129e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57389,10 +57389,10 @@
         <v>1</v>
       </c>
       <c r="JB71" t="n">
-        <v>0.9011568254762616</v>
+        <v>0.7836503946122937</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.7031282208417191</v>
+        <v>0.01448644464545336</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>7.621708635915141e-07</v>
+        <v>0</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58184,10 +58184,10 @@
         <v>1</v>
       </c>
       <c r="JB72" t="n">
-        <v>0.9011568254762616</v>
+        <v>0.7836503946122937</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.7031235724959429</v>
+        <v>0.01448653459010343</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>-2.975818632750635e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58979,10 +58979,10 @@
         <v>1</v>
       </c>
       <c r="JB73" t="n">
-        <v>0.9011568254762616</v>
+        <v>0.7836503946122937</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.7031168535961052</v>
+        <v>0.0144856766565186</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>0.9011568254762616</v>
+        <v>0.7836503946122937</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.70311708191714</v>
+        <v>0.01448590497755317</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>1</v>
       </c>
       <c r="JB75" t="n">
-        <v>0.9011568254762616</v>
+        <v>0.7836503946122937</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.7031162862529282</v>
+        <v>0.01448510931334144</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>1</v>
       </c>
       <c r="JB76" t="n">
-        <v>0.9011568254762616</v>
+        <v>0.7836503946122937</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.7031163485223013</v>
+        <v>0.01448517158271454</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>1</v>
       </c>
       <c r="JB77" t="n">
-        <v>0.9011568254762616</v>
+        <v>0.7836503946122937</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.7031163761975782</v>
+        <v>0.01448519925799151</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>1</v>
       </c>
       <c r="JB78" t="n">
-        <v>0.9011568254762616</v>
+        <v>0.7836503946122937</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.7031165284116014</v>
+        <v>0.01448535147201456</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>1</v>
       </c>
       <c r="JB79" t="n">
-        <v>0.9011568254762616</v>
+        <v>0.7836503946122937</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.7031161824706397</v>
+        <v>0.01448500553105294</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>0.9011568254762616</v>
+        <v>0.7836503946122937</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.7031162585776514</v>
+        <v>0.01448508163806458</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.9011568254762616</v>
+        <v>0.7836503946122937</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.7031164246293129</v>
+        <v>0.01448524768972618</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.9011568254762616</v>
+        <v>0.7836503946122937</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.703116784407913</v>
+        <v>0.01448560746832623</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.9011568254762616</v>
+        <v>0.7836503946122937</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.7031168051643707</v>
+        <v>0.01448562822478393</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.9011568254762616</v>
+        <v>0.7836503946122937</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.7031169089466592</v>
+        <v>0.01448573200707242</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.9011568254762616</v>
+        <v>0.7836503946122937</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.7031171372676939</v>
+        <v>0.01448596032810712</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>1</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.9011568254762616</v>
+        <v>0.7836503946122937</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.7031170127289477</v>
+        <v>0.01448583578936092</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.9011568254762616</v>
+        <v>0.7836503946122937</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.7031170404042245</v>
+        <v>0.01448586346463778</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.9011568254762616</v>
+        <v>0.7836503946122937</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.7031170957547784</v>
+        <v>0.01448591881519172</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.9011568254762616</v>
+        <v>0.7836503946122937</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.7031173586699092</v>
+        <v>0.01448618173032254</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.9011568254762616</v>
+        <v>0.7836503946122937</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.7031172756440783</v>
+        <v>0.01448609870449174</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>1</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.9011568254762616</v>
+        <v>0.7836503946122937</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.7031170680795016</v>
+        <v>0.01448589113991475</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.9011568254762616</v>
+        <v>0.7836503946122937</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.70311708191714</v>
+        <v>0.01448590497755317</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>1</v>
       </c>
       <c r="JB93" t="n">
-        <v>0.9011568254762616</v>
+        <v>0.7836503946122937</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.7031172202935246</v>
+        <v>0.01448604335393792</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.9011568254762616</v>
+        <v>0.7836503946122937</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.7031169366219361</v>
+        <v>0.01448575968234939</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>1</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.9011568254762616</v>
+        <v>0.7836503946122937</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.7031167636514553</v>
+        <v>0.01448558671186853</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>0.9011568254762616</v>
+        <v>0.7836503946122937</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.7031166598691668</v>
+        <v>0.01448548292958003</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>1</v>
       </c>
       <c r="JB97" t="n">
-        <v>0.9011568254762616</v>
+        <v>0.7836503946122937</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.7031168051643707</v>
+        <v>0.01448562822478393</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>1</v>
       </c>
       <c r="JB98" t="n">
-        <v>0.9011568254762616</v>
+        <v>0.7836503946122937</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.7031170473230439</v>
+        <v>0.01448587038345705</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>1</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.9011568254762616</v>
+        <v>0.7836503946122937</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.703116874352563</v>
+        <v>0.0144856974129763</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.9011568254762616</v>
+        <v>0.7836503946122937</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.7031165768433359</v>
+        <v>0.01448539990374923</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.9011568254762616</v>
+        <v>0.7836503946122937</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.7031165630056975</v>
+        <v>0.01448538606611081</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>1</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.9011568254762616</v>
+        <v>0.7836503946122937</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.7031161963082783</v>
+        <v>0.01448501936869149</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.9011568254762616</v>
+        <v>0.7836503946122937</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.7031161963082783</v>
+        <v>0.01448501936869149</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>1</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.9011568254762616</v>
+        <v>0.7836503946122937</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.7031161340389052</v>
+        <v>0.01448495709931839</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>1</v>
       </c>
       <c r="JB105" t="n">
-        <v>0.9011568254762616</v>
+        <v>0.7836503946122937</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.7031160302566166</v>
+        <v>0.01448485331702989</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>1</v>
       </c>
       <c r="JB106" t="n">
-        <v>0.9011568254762616</v>
+        <v>0.7836503946122937</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.7031158572861359</v>
+        <v>0.01448468034654902</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>1</v>
       </c>
       <c r="JB107" t="n">
-        <v>0.9011568254762616</v>
+        <v>0.7836503946122937</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.7031159057178704</v>
+        <v>0.01448472877828369</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>1</v>
       </c>
       <c r="JB108" t="n">
-        <v>0.9011568254762616</v>
+        <v>0.7836503946122937</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.7031155459392704</v>
+        <v>0.01448436899968353</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>0.9011568254762616</v>
+        <v>0.7836503946122937</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.703115504426355</v>
+        <v>0.01448432748676813</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>1</v>
       </c>
       <c r="JB110" t="n">
-        <v>0.9011568254762616</v>
+        <v>0.7836503946122937</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.7031155597769088</v>
+        <v>0.01448438283732208</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>1</v>
       </c>
       <c r="JB111" t="n">
-        <v>0.9011568254762616</v>
+        <v>0.7836503946122937</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.7031156151274627</v>
+        <v>0.0144844381878759</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>1</v>
       </c>
       <c r="JB112" t="n">
-        <v>0.9011568254762616</v>
+        <v>0.7836503946122937</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.703115656640378</v>
+        <v>0.0144844797007913</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>1</v>
       </c>
       <c r="JB113" t="n">
-        <v>0.9011568254762616</v>
+        <v>0.7836503946122937</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.7031153868064279</v>
+        <v>0.01448420986684121</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.9011568254762616</v>
+        <v>0.7836503946122937</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.703115442156982</v>
+        <v>0.01448426521739503</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>1</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.9011568254762616</v>
+        <v>0.7836503946122937</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.7031155874521858</v>
+        <v>0.01448441051259893</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.9011568254762616</v>
+        <v>0.7836503946122937</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.7031155528580896</v>
+        <v>0.0144843759185028</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>1</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.9011568254762616</v>
+        <v>0.7836503946122937</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.703115539020451</v>
+        <v>0.01448436208086437</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.9011568254762616</v>
+        <v>0.7836503946122937</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.7031156289651012</v>
+        <v>0.01448445202551433</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.9011568254762616</v>
+        <v>0.7836503946122937</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.7031159472307859</v>
+        <v>0.01448477029119909</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>1</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.9011568254762616</v>
+        <v>0.7836503946122937</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.7031157673414857</v>
+        <v>0.01448459040189907</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>1</v>
       </c>
       <c r="JB121" t="n">
-        <v>0.9011568254762616</v>
+        <v>0.7836503946122937</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.7031158088544011</v>
+        <v>0.01448463191481447</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>1</v>
       </c>
       <c r="JB122" t="n">
-        <v>0.9011568254762616</v>
+        <v>0.7836503946122937</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.7031156220462819</v>
+        <v>0.01448444510669517</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>1</v>
       </c>
       <c r="JB123" t="n">
-        <v>0.9011568254762616</v>
+        <v>0.7836503946122937</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.7031156912344743</v>
+        <v>0.01448451429488743</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>1</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.9011568254762616</v>
+        <v>0.7836503946122937</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.7031154905887165</v>
+        <v>0.01448431364912971</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>1</v>
       </c>
       <c r="JB125" t="n">
-        <v>0.9011568254762616</v>
+        <v>0.7836503946122937</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.7031155321016319</v>
+        <v>0.0144843551620451</v>
       </c>
     </row>
     <row r="126">
@@ -101103,7 +101103,7 @@
         <v>0</v>
       </c>
       <c r="IY126" t="n">
-        <v>-4.268085246219792e-06</v>
+        <v>-3.873712549958921e-06</v>
       </c>
       <c r="IZ126" t="inlineStr">
         <is>
@@ -101114,10 +101114,10 @@
         <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>0.9011568254762616</v>
+        <v>0.7836503946122937</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.7031155597769088</v>
+        <v>0.01448438283732208</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-mamba2_repeat_2_000006.xlsx
+++ b/out/Attention-mamba2_repeat_2_000006.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>-0.1544381380081177</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.158921290794059</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>-0.1458210647106171</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.158921290794059</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>-0.176552802324295</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.158921290794059</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>-0.2367135733366013</v>
       </c>
       <c r="JB5" t="n">
-        <v>-1.158921290794059</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>-0.1584025472402573</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.158921290794059</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>-0.1882644444704056</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.158921290794059</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>-0.07785426080226898</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.158921290794059</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>-0.2123248726129532</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.158921290794059</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>-0.2365090548992157</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.158921290794059</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>-0.150939866900444</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.158921290794059</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>-0.07807137072086334</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.158921290794059</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>-0.04242109507322311</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.158921290794059</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>-0.1189662888646126</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.158921290794059</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>-0.05786549299955368</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.158921290794059</v>
+        <v>0.16</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13657,14 +13657,14 @@
       </c>
       <c r="IZ16" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>-0.04698579385876656</v>
       </c>
       <c r="JB16" t="n">
-        <v>-1.158921290794059</v>
+        <v>0.3</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14452,14 +14452,14 @@
       </c>
       <c r="IZ17" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>-0.04420351609587669</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.158921290794059</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>-0.08007010817527771</v>
       </c>
       <c r="JB18" t="n">
-        <v>-1.158921290794059</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>-0.1299696564674377</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.158921290794059</v>
+        <v>0.3</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>-0.2599847614765167</v>
       </c>
       <c r="JB20" t="n">
-        <v>-1.158921290794059</v>
+        <v>0.16</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>-0.1379272490739822</v>
       </c>
       <c r="JB21" t="n">
-        <v>-1.158921290794059</v>
+        <v>0.3</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>-0.1132286936044693</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.158921290794059</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19222,14 +19222,14 @@
       </c>
       <c r="IZ23" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>-0.05580418556928635</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.158921290794059</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20017,14 +20017,14 @@
       </c>
       <c r="IZ24" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>-0.06399135291576385</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.158921290794059</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0</v>
+        <v>-0.1909948289394379</v>
       </c>
       <c r="JB25" t="n">
-        <v>-1.158921290794059</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>-0.08353466540575027</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.158921290794059</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>-0.2068931311368942</v>
       </c>
       <c r="JB27" t="n">
-        <v>-1.158921290794059</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>-0.3889304995536804</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.158921290794059</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>-0.4415722787380219</v>
       </c>
       <c r="JB29" t="n">
-        <v>-1.158921290794059</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>-0.2714961469173431</v>
       </c>
       <c r="JB30" t="n">
-        <v>-1.158921290794059</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>-0.2529376745223999</v>
       </c>
       <c r="JB31" t="n">
-        <v>-1.158921290794059</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>-0.08551882952451706</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.158921290794059</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>-0.03787592425942421</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.158921290794059</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>-0.06500710546970367</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.158921290794059</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>-0.4399063587188721</v>
       </c>
       <c r="JB35" t="n">
-        <v>-1.158921290794059</v>
+        <v>0.16</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>-0.3009251654148102</v>
       </c>
       <c r="JB36" t="n">
-        <v>-1.158921290794059</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>-0.2524468898773193</v>
       </c>
       <c r="JB37" t="n">
-        <v>-1.158921290794059</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>-0.3728805482387543</v>
       </c>
       <c r="JB38" t="n">
-        <v>-1.158921290794059</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>-0.1669049561023712</v>
       </c>
       <c r="JB39" t="n">
-        <v>-1.158921290794059</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>-0.2139166295528412</v>
       </c>
       <c r="JB40" t="n">
-        <v>-1.158921290794059</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>-0.3591267764568329</v>
       </c>
       <c r="JB41" t="n">
-        <v>-1.158921290794059</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0</v>
+        <v>-0.3678728640079498</v>
       </c>
       <c r="JB42" t="n">
-        <v>-1.158921290794059</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35122,14 +35122,14 @@
       </c>
       <c r="IZ43" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0</v>
+        <v>-0.2063621282577515</v>
       </c>
       <c r="JB43" t="n">
-        <v>-1.158921290794059</v>
+        <v>0.16</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35917,17 +35917,17 @@
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Buy</t>
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0</v>
+        <v>-0.1367597430944443</v>
       </c>
       <c r="JB44" t="n">
-        <v>-1.158921290794059</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC44" t="n">
-        <v>0</v>
+        <v>-0.0001505071560592624</v>
       </c>
     </row>
     <row r="45">
@@ -36708,21 +36708,21 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0</v>
+        <v>0.1937144337915407</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>TakeProfit</t>
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0</v>
+        <v>-0.09983499348163605</v>
       </c>
       <c r="JB45" t="n">
-        <v>-1.158921290794059</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC45" t="n">
-        <v>0</v>
+        <v>0.3877954684738684</v>
       </c>
     </row>
     <row r="46">
@@ -37503,21 +37503,21 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0</v>
+        <v>-0.04473662505144678</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>StopLoss</t>
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>-0.1055351570248604</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.158921290794059</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC46" t="n">
-        <v>0</v>
+        <v>0.1488273015840347</v>
       </c>
     </row>
     <row r="47">
@@ -38302,17 +38302,17 @@
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0</v>
+        <v>-0.02714405581355095</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.158921290794059</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC47" t="n">
-        <v>0</v>
+        <v>0.1488273015840347</v>
       </c>
     </row>
     <row r="48">
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>-0.117363877594471</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.158921290794059</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC48" t="n">
-        <v>-5.933721306733787e-06</v>
+        <v>0.1486156038082694</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.007169178160520064</v>
+        <v>0.6503811886158382</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>-0.0539282038807869</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.158921290794059</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.01434917160715582</v>
+        <v>1.450673367183232</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.001367976758648252</v>
+        <v>0.124443112171669</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>-0.09010687470436096</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.158921290794059</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.009907249804488849</v>
+        <v>1.048229098202003</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.002399242476805734</v>
+        <v>0.2179739129156838</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>-0.06803414970636368</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.158921290794059</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.01333873167907086</v>
+        <v>1.359795124265163</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.001311642320319503</v>
+        <v>0.1193706851751525</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>-0.08625604957342148</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.3113973956586084</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.01356115812523325</v>
+        <v>1.380374265908879</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.000538800078243116</v>
+        <v>0.04930163459558872</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0.02793876081705093</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.3113973956586084</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.01332592913946242</v>
+        <v>1.359482106234268</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0006729861208765089</v>
+        <v>0.0614260963449625</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>-0.0549083799123764</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.3361264994768428</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.01413278057485225</v>
+        <v>1.433040545830615</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0004026421962169791</v>
+        <v>0.03698644455388703</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0.1085760444402695</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.3113973956586084</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.01426589324904222</v>
+        <v>1.445545654895101</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.0003058131087535019</v>
+        <v>0.028118742844101</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>-0.02163020521402359</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.3361264994768428</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.01447355598816136</v>
+        <v>1.464782688733796</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.0001316791176383418</v>
+        <v>0.01243597828922023</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0.09500604867935181</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.3361264994768428</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.01443247218956053</v>
+        <v>1.461511909542022</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.0001034551079699113</v>
+        <v>0.009866937037075181</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0.02604330331087112</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.9836503946122938</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.01450859796156152</v>
+        <v>1.468807156064419</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>5.003256579271103e-05</v>
+        <v>0.004890396875287977</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.0297255739569664</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.9836503946122938</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.01450261576684681</v>
+        <v>1.468714764623559</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>2.700120820192495e-05</v>
+        <v>0.002843107529971321</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0.02343064546585083</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.9836503946122938</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.01450655655054632</v>
+        <v>1.469505494372815</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>9.546003728147707e-06</v>
+        <v>0.001417599164612846</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0.08787482976913452</v>
       </c>
       <c r="JB61" t="n">
-        <v>0.9836503946122938</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.01450153843978979</v>
+        <v>1.469498723140822</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>3.623944487145107e-06</v>
+        <v>0.0006992887997835171</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0.1075772494077682</v>
       </c>
       <c r="JB62" t="n">
-        <v>0.9836503946122938</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.01449632013329759</v>
+        <v>1.469475894777295</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>-1.662347222097263e-06</v>
+        <v>0.0004021936389041338</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0.08182619512081146</v>
       </c>
       <c r="JB63" t="n">
-        <v>0.9836503946122938</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.01449270667905186</v>
+        <v>1.4695839624918</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>-2.768029886028092e-06</v>
+        <v>0.0001311501769522864</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>1</v>
+        <v>0.1215196251869202</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.9836503946122938</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.0144854898483993</v>
+        <v>1.469442628810912</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0</v>
+        <v>6.461952556540234e-05</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.1229705810546875</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.9836503946122938</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.01448550368603773</v>
+        <v>1.469438399166293</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0</v>
+        <v>3.169294195162759e-05</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0.1193453967571259</v>
       </c>
       <c r="JB66" t="n">
-        <v>0.9836503946122938</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.01448570433179545</v>
+        <v>1.46943957319661</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0</v>
+        <v>1.396144357570609e-05</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.1277644038200378</v>
       </c>
       <c r="JB67" t="n">
-        <v>0.7836503946122937</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.01448562822478393</v>
+        <v>1.469433331688026</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0</v>
+        <v>6.636802982518164e-06</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>1</v>
+        <v>0.1195332258939743</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.7836503946122937</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.01448616789268411</v>
+        <v>1.469432634542623</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0</v>
+        <v>1.549918929005845e-07</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0.1269426345825195</v>
       </c>
       <c r="JB69" t="n">
-        <v>0.7836503946122937</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.01448583578936092</v>
+        <v>1.469426299682075</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0</v>
+        <v>-2.042425637823487e-06</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0.1239727735519409</v>
       </c>
       <c r="JB70" t="n">
-        <v>0.7836503946122937</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.01448621632441867</v>
+        <v>1.469422057071921</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>1</v>
+        <v>0.1145900338888168</v>
       </c>
       <c r="JB71" t="n">
-        <v>0.7836503946122937</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.01448644464545336</v>
+        <v>1.469422285392956</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>1</v>
+        <v>0.1225547343492508</v>
       </c>
       <c r="JB72" t="n">
-        <v>0.7836503946122937</v>
+        <v>-0.16</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.01448653459010343</v>
+        <v>1.469422375337606</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>0.1151917576789856</v>
       </c>
       <c r="JB73" t="n">
-        <v>0.7836503946122937</v>
+        <v>-0.3</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.0144856766565186</v>
+        <v>1.469421517404021</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0.126730352640152</v>
       </c>
       <c r="JB74" t="n">
-        <v>0.7836503946122937</v>
+        <v>-0.3</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.01448590497755317</v>
+        <v>1.469421745725056</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>1</v>
+        <v>0.1174194365739822</v>
       </c>
       <c r="JB75" t="n">
-        <v>0.7836503946122937</v>
+        <v>-0.3</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.01448510931334144</v>
+        <v>1.469420950060844</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0.1121200770139694</v>
       </c>
       <c r="JB76" t="n">
-        <v>0.7836503946122937</v>
+        <v>-0.16</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.01448517158271454</v>
+        <v>1.469421012330217</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0.113911509513855</v>
       </c>
       <c r="JB77" t="n">
-        <v>0.7836503946122937</v>
+        <v>-0.16</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.01448519925799151</v>
+        <v>1.469421040005494</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0.1240866184234619</v>
       </c>
       <c r="JB78" t="n">
-        <v>0.7836503946122937</v>
+        <v>-0.16</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.01448535147201456</v>
+        <v>1.469421192219517</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>1</v>
+        <v>0.1127874702215195</v>
       </c>
       <c r="JB79" t="n">
-        <v>0.7836503946122937</v>
+        <v>-0.16</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.01448500553105294</v>
+        <v>1.469420846278556</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0.1093562245368958</v>
       </c>
       <c r="JB80" t="n">
-        <v>0.7836503946122937</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.01448508163806458</v>
+        <v>1.469420922385567</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0.07885172963142395</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.7836503946122937</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.01448524768972618</v>
+        <v>1.469421088437229</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0.1233917027711868</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.7836503946122937</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.01448560746832623</v>
+        <v>1.469421448215829</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0.1286185681819916</v>
       </c>
       <c r="JB83" t="n">
-        <v>0.7836503946122937</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.01448562822478393</v>
+        <v>1.469421468972287</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0.1249295026063919</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.7836503946122937</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.01448573200707242</v>
+        <v>1.469421572754575</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0.1109867841005325</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.7836503946122937</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.01448596032810712</v>
+        <v>1.46942180107561</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>1</v>
+        <v>0.08967211842536926</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.7836503946122937</v>
+        <v>-0.3</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.01448583578936092</v>
+        <v>1.469421676536864</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0.05787215381860733</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.7836503946122937</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.01448586346463778</v>
+        <v>1.469421704212141</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.1142780333757401</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.7836503946122937</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.01448591881519172</v>
+        <v>1.469421759562694</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0.1003818958997726</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.7836503946122937</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.01448618173032254</v>
+        <v>1.469422022477825</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0.09472367167472839</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.7836503946122937</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.01448609870449174</v>
+        <v>1.469421939451994</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0.07490748167037964</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.7836503946122937</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.01448589113991475</v>
+        <v>1.469421731887417</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0.06866241991519928</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.7836503946122937</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.01448590497755317</v>
+        <v>1.469421745725056</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>1</v>
+        <v>0.07032811641693115</v>
       </c>
       <c r="JB93" t="n">
-        <v>0.7836503946122937</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.01448604335393792</v>
+        <v>1.469421884101441</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0.06969055533409119</v>
       </c>
       <c r="JB94" t="n">
-        <v>0.7836503946122937</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.01448575968234939</v>
+        <v>1.469421600429852</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>1</v>
+        <v>0.05086024105548859</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.7836503946122937</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.01448558671186853</v>
+        <v>1.469421427459371</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0.09190917015075684</v>
       </c>
       <c r="JB96" t="n">
-        <v>0.7836503946122937</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.01448548292958003</v>
+        <v>1.469421323677083</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0.07209713757038116</v>
       </c>
       <c r="JB97" t="n">
-        <v>0.7836503946122937</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.01448562822478393</v>
+        <v>1.469421468972287</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>1</v>
+        <v>0.05599900335073471</v>
       </c>
       <c r="JB98" t="n">
-        <v>0.7836503946122937</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.01448587038345705</v>
+        <v>1.46942171113096</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0.07262274622917175</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.7836503946122937</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.0144856974129763</v>
+        <v>1.469421538160479</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0.04197688400745392</v>
       </c>
       <c r="JB100" t="n">
-        <v>0.7836503946122937</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.01448539990374923</v>
+        <v>1.469421240651252</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0.07517622411251068</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.7836503946122937</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.01448538606611081</v>
+        <v>1.469421226813614</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0.04714910686016083</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.7836503946122937</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.01448501936869149</v>
+        <v>1.469420860116194</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0.06551635265350342</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.7836503946122937</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.01448501936869149</v>
+        <v>1.469420860116194</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0.1215920001268387</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.7836503946122937</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.01448495709931839</v>
+        <v>1.469420797846821</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>1</v>
+        <v>0.065299391746521</v>
       </c>
       <c r="JB105" t="n">
-        <v>0.7836503946122937</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.01448485331702989</v>
+        <v>1.469420694064532</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>1</v>
+        <v>0.05896015465259552</v>
       </c>
       <c r="JB106" t="n">
-        <v>0.7836503946122937</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.01448468034654902</v>
+        <v>1.469420521094052</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>1</v>
+        <v>0.08447001874446869</v>
       </c>
       <c r="JB107" t="n">
-        <v>0.7836503946122937</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.01448472877828369</v>
+        <v>1.469420569525786</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>1</v>
+        <v>0.06497544050216675</v>
       </c>
       <c r="JB108" t="n">
-        <v>0.7836503946122937</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.01448436899968353</v>
+        <v>1.469420209747186</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>1</v>
+        <v>0.03285772353410721</v>
       </c>
       <c r="JB109" t="n">
-        <v>0.7836503946122937</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.01448432748676813</v>
+        <v>1.469420168234271</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>1</v>
+        <v>0.08184598386287689</v>
       </c>
       <c r="JB110" t="n">
-        <v>0.7836503946122937</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.01448438283732208</v>
+        <v>1.469420223584825</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>1</v>
+        <v>0.03089819848537445</v>
       </c>
       <c r="JB111" t="n">
-        <v>0.7836503946122937</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.0144844381878759</v>
+        <v>1.469420278935379</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>1</v>
+        <v>0.03772711753845215</v>
       </c>
       <c r="JB112" t="n">
-        <v>0.7836503946122937</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.0144844797007913</v>
+        <v>1.469420320448294</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>1</v>
+        <v>0.02560999244451523</v>
       </c>
       <c r="JB113" t="n">
-        <v>0.7836503946122937</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.01448420986684121</v>
+        <v>1.469420050614344</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0.02638468891382217</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.7836503946122937</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.01448426521739503</v>
+        <v>1.469420105964898</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0.02851010113954544</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.7836503946122937</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.01448441051259893</v>
+        <v>1.469420251260102</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0.02760164439678192</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.7836503946122937</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.0144843759185028</v>
+        <v>1.469420216666006</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>1</v>
+        <v>0.01872124522924423</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.7836503946122937</v>
+        <v>0.16</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.01448436208086437</v>
+        <v>1.469420202828367</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0.09850198030471802</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.7836503946122937</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.01448445202551433</v>
+        <v>1.469420292773017</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0.1050640344619751</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.7836503946122937</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.01448477029119909</v>
+        <v>1.469420611038702</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0.1240935325622559</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.7836503946122937</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.01448459040189907</v>
+        <v>1.469420431149402</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0.1077306270599365</v>
       </c>
       <c r="JB121" t="n">
-        <v>0.7836503946122937</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.01448463191481447</v>
+        <v>1.469420472662317</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0.09270629286766052</v>
       </c>
       <c r="JB122" t="n">
-        <v>0.7836503946122937</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.01448444510669517</v>
+        <v>1.469420285854198</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0.06164383888244629</v>
       </c>
       <c r="JB123" t="n">
-        <v>0.7836503946122937</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.01448451429488743</v>
+        <v>1.46942035504239</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0.08111986517906189</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.7836503946122937</v>
+        <v>0.3</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.01448431364912971</v>
+        <v>1.469420154396633</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>1</v>
+        <v>0.04323892295360565</v>
       </c>
       <c r="JB125" t="n">
-        <v>0.7836503946122937</v>
+        <v>-0.5100000000000003</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.0144843551620451</v>
+        <v>1.469420195909548</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0.0832417905330658</v>
       </c>
       <c r="JB126" t="n">
-        <v>0.7836503946122937</v>
+        <v>-0.7200000000000004</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.01448438283732208</v>
+        <v>1.469420223584825</v>
       </c>
     </row>
   </sheetData>

--- a/out/Attention-mamba2_repeat_2_000006.xlsx
+++ b/out/Attention-mamba2_repeat_2_000006.xlsx
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>-0.1544381380081177</v>
+        <v>-0.1544400304555893</v>
       </c>
       <c r="JB2" t="n">
         <v>-0.9999999999999998</v>
@@ -3326,7 +3326,7 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>-0.1458210647106171</v>
+        <v>-0.1458372175693512</v>
       </c>
       <c r="JB3" t="n">
         <v>-0.9999999999999998</v>
@@ -4121,7 +4121,7 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>-0.176552802324295</v>
+        <v>-0.1765658408403397</v>
       </c>
       <c r="JB4" t="n">
         <v>-0.9999999999999998</v>
@@ -4916,7 +4916,7 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>-0.2367135733366013</v>
+        <v>-0.2367157787084579</v>
       </c>
       <c r="JB5" t="n">
         <v>-0.9999999999999998</v>
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>-0.1584025472402573</v>
+        <v>-0.158423900604248</v>
       </c>
       <c r="JB6" t="n">
         <v>-0.9999999999999998</v>
@@ -6506,7 +6506,7 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>-0.1882644444704056</v>
+        <v>-0.1882789731025696</v>
       </c>
       <c r="JB7" t="n">
         <v>-0.9999999999999998</v>
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>-0.07785426080226898</v>
+        <v>-0.07786719501018524</v>
       </c>
       <c r="JB8" t="n">
         <v>-0.9999999999999998</v>
@@ -8096,7 +8096,7 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>-0.2123248726129532</v>
+        <v>-0.2123104929924011</v>
       </c>
       <c r="JB9" t="n">
         <v>-0.9999999999999998</v>
@@ -8891,7 +8891,7 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>-0.2365090548992157</v>
+        <v>-0.2364873886108398</v>
       </c>
       <c r="JB10" t="n">
         <v>-0.9999999999999998</v>
@@ -9686,7 +9686,7 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>-0.150939866900444</v>
+        <v>-0.150932639837265</v>
       </c>
       <c r="JB11" t="n">
         <v>-0.9999999999999998</v>
@@ -10481,7 +10481,7 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>-0.07807137072086334</v>
+        <v>-0.07807604223489761</v>
       </c>
       <c r="JB12" t="n">
         <v>-0.9999999999999998</v>
@@ -11276,7 +11276,7 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>-0.04242109507322311</v>
+        <v>-0.04242916405200958</v>
       </c>
       <c r="JB13" t="n">
         <v>-0.9999999999999998</v>
@@ -12071,7 +12071,7 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>-0.1189662888646126</v>
+        <v>-0.1189565807580948</v>
       </c>
       <c r="JB14" t="n">
         <v>-0.1199999999999999</v>
@@ -12866,7 +12866,7 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>-0.05786549299955368</v>
+        <v>-0.05786590278148651</v>
       </c>
       <c r="JB15" t="n">
         <v>0.16</v>
@@ -13661,7 +13661,7 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>-0.04698579385876656</v>
+        <v>-0.04698934033513069</v>
       </c>
       <c r="JB16" t="n">
         <v>0.3</v>
@@ -14456,7 +14456,7 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>-0.04420351609587669</v>
+        <v>-0.04421142861247063</v>
       </c>
       <c r="JB17" t="n">
         <v>0.4399999999999999</v>
@@ -15251,7 +15251,7 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>-0.08007010817527771</v>
+        <v>-0.08007484674453735</v>
       </c>
       <c r="JB18" t="n">
         <v>0.4399999999999999</v>
@@ -16046,7 +16046,7 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>-0.1299696564674377</v>
+        <v>-0.1299638152122498</v>
       </c>
       <c r="JB19" t="n">
         <v>0.3</v>
@@ -16841,7 +16841,7 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>-0.2599847614765167</v>
+        <v>-0.2599381506443024</v>
       </c>
       <c r="JB20" t="n">
         <v>0.16</v>
@@ -17636,7 +17636,7 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>-0.1379272490739822</v>
+        <v>-0.1379100978374481</v>
       </c>
       <c r="JB21" t="n">
         <v>0.3</v>
@@ -18431,7 +18431,7 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>-0.1132286936044693</v>
+        <v>-0.1132175549864769</v>
       </c>
       <c r="JB22" t="n">
         <v>0.4399999999999999</v>
@@ -19226,7 +19226,7 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>-0.05580418556928635</v>
+        <v>-0.05580618605017662</v>
       </c>
       <c r="JB23" t="n">
         <v>0.4399999999999999</v>
@@ -20021,7 +20021,7 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>-0.06399135291576385</v>
+        <v>-0.06400122493505478</v>
       </c>
       <c r="JB24" t="n">
         <v>0.5799999999999998</v>
@@ -20816,7 +20816,7 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>-0.1909948289394379</v>
+        <v>-0.1909665465354919</v>
       </c>
       <c r="JB25" t="n">
         <v>0.4399999999999999</v>
@@ -21611,7 +21611,7 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>-0.08353466540575027</v>
+        <v>-0.08353588730096817</v>
       </c>
       <c r="JB26" t="n">
         <v>0.1600000000000001</v>
@@ -22406,7 +22406,7 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>-0.2068931311368942</v>
+        <v>-0.2068704217672348</v>
       </c>
       <c r="JB27" t="n">
         <v>-0.7199999999999999</v>
@@ -23201,7 +23201,7 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>-0.3889304995536804</v>
+        <v>-0.3888299465179443</v>
       </c>
       <c r="JB28" t="n">
         <v>-0.7199999999999999</v>
@@ -23996,7 +23996,7 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>-0.4415722787380219</v>
+        <v>-0.441494345664978</v>
       </c>
       <c r="JB29" t="n">
         <v>-0.9999999999999998</v>
@@ -24791,7 +24791,7 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>-0.2714961469173431</v>
+        <v>-0.2714453935623169</v>
       </c>
       <c r="JB30" t="n">
         <v>-0.7199999999999999</v>
@@ -25586,7 +25586,7 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>-0.2529376745223999</v>
+        <v>-0.2528878748416901</v>
       </c>
       <c r="JB31" t="n">
         <v>-0.4399999999999999</v>
@@ -26381,7 +26381,7 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>-0.08551882952451706</v>
+        <v>-0.06810075044631958</v>
       </c>
       <c r="JB32" t="n">
         <v>0.4399999999999999</v>
@@ -27176,7 +27176,7 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>-0.03787592425942421</v>
+        <v>-0.03784536942839622</v>
       </c>
       <c r="JB33" t="n">
         <v>0.4399999999999999</v>
@@ -27971,7 +27971,7 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>-0.06500710546970367</v>
+        <v>-0.06502075493335724</v>
       </c>
       <c r="JB34" t="n">
         <v>0.4399999999999999</v>
@@ -28766,7 +28766,7 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>-0.4399063587188721</v>
+        <v>-0.4398161768913269</v>
       </c>
       <c r="JB35" t="n">
         <v>0.16</v>
@@ -29561,7 +29561,7 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>-0.3009251654148102</v>
+        <v>-0.3008739948272705</v>
       </c>
       <c r="JB36" t="n">
         <v>-0.1199999999999999</v>
@@ -30356,7 +30356,7 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>-0.2524468898773193</v>
+        <v>-0.2524039745330811</v>
       </c>
       <c r="JB37" t="n">
         <v>-0.8599999999999999</v>
@@ -31151,7 +31151,7 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>-0.3728805482387543</v>
+        <v>-0.3728117942810059</v>
       </c>
       <c r="JB38" t="n">
         <v>-0.8599999999999999</v>
@@ -31946,7 +31946,7 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>-0.1669049561023712</v>
+        <v>-0.1668807566165924</v>
       </c>
       <c r="JB39" t="n">
         <v>-0.8599999999999999</v>
@@ -32741,7 +32741,7 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>-0.2139166295528412</v>
+        <v>-0.2138799279928207</v>
       </c>
       <c r="JB40" t="n">
         <v>-0.8599999999999999</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>-0.3591267764568329</v>
+        <v>-0.3590541183948517</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.8599999999999999</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>-0.3678728640079498</v>
+        <v>-0.3677680492401123</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.7199999999999999</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>-0.2063621282577515</v>
+        <v>-0.1793054342269897</v>
       </c>
       <c r="JB43" t="n">
-        <v>0.16</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>-0.1367597430944443</v>
+        <v>-0.1366536766290665</v>
       </c>
       <c r="JB44" t="n">
-        <v>0.4399999999999999</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC44" t="n">
-        <v>-0.0001505071560592624</v>
+        <v>-0.0001826481971237809</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.1937144337915407</v>
+        <v>0.2350824573080914</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>-0.09983499348163605</v>
+        <v>-0.09980727732181549</v>
       </c>
       <c r="JB45" t="n">
-        <v>0.7199999999999999</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.3877954684738684</v>
+        <v>0.4706098037066381</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.04473662505144678</v>
+        <v>-0.05429020204081502</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>-0.1055351570248604</v>
+        <v>-0.1055057421326637</v>
       </c>
       <c r="JB46" t="n">
         <v>0.9999999999999998</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.1488273015840347</v>
+        <v>0.1806096070701526</v>
       </c>
     </row>
     <row r="47">
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>-0.02714405581355095</v>
+        <v>-0.02718190848827362</v>
       </c>
       <c r="JB47" t="n">
         <v>0.9999999999999998</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.1488273015840347</v>
+        <v>0.1806096070701526</v>
       </c>
     </row>
     <row r="48">
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>-0.117363877594471</v>
+        <v>-0.1172985136508942</v>
       </c>
       <c r="JB48" t="n">
         <v>0.9999999999999998</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.1486156038082694</v>
+        <v>0.1803920526994146</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.6503811886158382</v>
+        <v>0.6683739149748819</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>-0.0539282038807869</v>
+        <v>-0.0538785308599472</v>
       </c>
       <c r="JB49" t="n">
         <v>0.9999999999999998</v>
       </c>
       <c r="JC49" t="n">
-        <v>1.450673367183232</v>
+        <v>1.518471096516048</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.124443112171669</v>
+        <v>0.1278858797214048</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>-0.09010687470436096</v>
+        <v>-0.09011650830507278</v>
       </c>
       <c r="JB50" t="n">
         <v>0.8599999999999999</v>
       </c>
       <c r="JC50" t="n">
-        <v>1.048229098202003</v>
+        <v>1.104893255046249</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.2179739129156838</v>
+        <v>0.2240040292478788</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>-0.06803414970636368</v>
+        <v>-0.06799058616161346</v>
       </c>
       <c r="JB51" t="n">
         <v>0.8599999999999999</v>
       </c>
       <c r="JC51" t="n">
-        <v>1.359795124265163</v>
+        <v>1.425078557974845</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.1193706851751525</v>
+        <v>0.1226729963181879</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>-0.08625604957342148</v>
+        <v>-0.08624234795570374</v>
       </c>
       <c r="JB52" t="n">
-        <v>0.7199999999999999</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC52" t="n">
-        <v>1.380374265908879</v>
+        <v>1.446227007976508</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.04930163459558872</v>
+        <v>0.05066553719016853</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0.02793876081705093</v>
+        <v>0.02795659005641937</v>
       </c>
       <c r="JB53" t="n">
         <v>0.1199999999999999</v>
       </c>
       <c r="JC53" t="n">
-        <v>1.359482106234268</v>
+        <v>1.424756880496547</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0614260963449625</v>
+        <v>0.06312491151549032</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>-0.0549083799123764</v>
+        <v>-0.05489004403352737</v>
       </c>
       <c r="JB54" t="n">
         <v>0.1199999999999999</v>
       </c>
       <c r="JC54" t="n">
-        <v>1.433040545830615</v>
+        <v>1.500350258420563</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.03698644455388703</v>
+        <v>0.03800935072652031</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0.1085760444402695</v>
+        <v>0.1085530519485474</v>
       </c>
       <c r="JB55" t="n">
         <v>0.2599999999999998</v>
       </c>
       <c r="JC55" t="n">
-        <v>1.445545654895101</v>
+        <v>1.513201412490971</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.028118742844101</v>
+        <v>0.02889822255758719</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>-0.02163020521402359</v>
+        <v>-0.02164502441883087</v>
       </c>
       <c r="JB56" t="n">
         <v>0.1199999999999999</v>
       </c>
       <c r="JC56" t="n">
-        <v>1.464782688733796</v>
+        <v>1.532971083329388</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.01243597828922023</v>
+        <v>0.0127808546674472</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0.09500604867935181</v>
+        <v>0.09494426846504211</v>
       </c>
       <c r="JB57" t="n">
         <v>0.2599999999999998</v>
       </c>
       <c r="JC57" t="n">
-        <v>1.461511909542022</v>
+        <v>1.529609986786109</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.009866937037075181</v>
+        <v>0.01013933591290659</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0.02604330331087112</v>
+        <v>0.0259968489408493</v>
       </c>
       <c r="JB58" t="n">
         <v>0.1199999999999999</v>
       </c>
       <c r="JC58" t="n">
-        <v>1.468807156064419</v>
+        <v>1.537106645099009</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.004890396875287977</v>
+        <v>0.00502547680950645</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0.0297255739569664</v>
+        <v>0.02979343384504318</v>
       </c>
       <c r="JB59" t="n">
         <v>0.1199999999999999</v>
       </c>
       <c r="JC59" t="n">
-        <v>1.468714764623559</v>
+        <v>1.537011842816576</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.002843107529971321</v>
+        <v>0.002921655950103318</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0.02343064546585083</v>
+        <v>0.02345038950443268</v>
       </c>
       <c r="JB60" t="n">
         <v>0.1199999999999999</v>
       </c>
       <c r="JC60" t="n">
-        <v>1.469505494372815</v>
+        <v>1.537824518125823</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.001417599164612846</v>
+        <v>0.001458327975051659</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0.08787482976913452</v>
+        <v>0.0878603458404541</v>
       </c>
       <c r="JB61" t="n">
         <v>0.8599999999999999</v>
       </c>
       <c r="JC61" t="n">
-        <v>1.469498723140822</v>
+        <v>1.537817696183712</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.0006992887997835171</v>
+        <v>0.0007165366887578073</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0.1075772494077682</v>
+        <v>0.1075573265552521</v>
       </c>
       <c r="JB62" t="n">
         <v>0.8599999999999999</v>
       </c>
       <c r="JC62" t="n">
-        <v>1.469475894777295</v>
+        <v>1.537794396613103</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.0004021936389041338</v>
+        <v>0.0004155442500157448</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0.08182619512081146</v>
+        <v>0.08181068301200867</v>
       </c>
       <c r="JB63" t="n">
         <v>0.9999999999999998</v>
       </c>
       <c r="JC63" t="n">
-        <v>1.4695839624918</v>
+        <v>1.537905692706182</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.0001311501769522864</v>
+        <v>0.0001356141171802302</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0.1215196251869202</v>
+        <v>0.1214892715215683</v>
       </c>
       <c r="JB64" t="n">
         <v>0.9999999999999998</v>
       </c>
       <c r="JC64" t="n">
-        <v>1.469442628810912</v>
+        <v>1.537761032375068</v>
       </c>
     </row>
     <row r="65">
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0.1229705810546875</v>
+        <v>0.1229299306869507</v>
       </c>
       <c r="JB65" t="n">
         <v>0.9999999999999998</v>
       </c>
       <c r="JC65" t="n">
-        <v>1.469438399166293</v>
+        <v>1.537756816568087</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>3.169294195162759e-05</v>
+        <v>3.41391380817361e-05</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0.1193453967571259</v>
+        <v>0.1192981749773026</v>
       </c>
       <c r="JB66" t="n">
         <v>0.9999999999999998</v>
       </c>
       <c r="JC66" t="n">
-        <v>1.46943957319661</v>
+        <v>1.537758188178283</v>
       </c>
     </row>
     <row r="67">
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0.1277644038200378</v>
+        <v>0.1277216076850891</v>
       </c>
       <c r="JB67" t="n">
         <v>0.9999999999999998</v>
       </c>
       <c r="JC67" t="n">
-        <v>1.469433331688026</v>
+        <v>1.5377519466697</v>
       </c>
     </row>
     <row r="68">
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0.1195332258939743</v>
+        <v>0.119499072432518</v>
       </c>
       <c r="JB68" t="n">
         <v>0.9999999999999998</v>
       </c>
       <c r="JC68" t="n">
-        <v>1.469432634542623</v>
+        <v>1.537751249524296</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0.1269426345825195</v>
+        <v>0.1269005686044693</v>
       </c>
       <c r="JB69" t="n">
         <v>0.8599999999999999</v>
       </c>
       <c r="JC69" t="n">
-        <v>1.469426299682075</v>
+        <v>1.537744914663748</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0.1239727735519409</v>
+        <v>0.1239284723997116</v>
       </c>
       <c r="JB70" t="n">
         <v>0.1199999999999999</v>
       </c>
       <c r="JC70" t="n">
-        <v>1.469422057071921</v>
+        <v>1.537740672053595</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0.1145900338888168</v>
+        <v>0.1145403385162354</v>
       </c>
       <c r="JB71" t="n">
         <v>-0.02000000000000007</v>
       </c>
       <c r="JC71" t="n">
-        <v>1.469422285392956</v>
+        <v>1.53774090037463</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0.1225547343492508</v>
+        <v>0.1225059181451797</v>
       </c>
       <c r="JB72" t="n">
         <v>-0.16</v>
       </c>
       <c r="JC72" t="n">
-        <v>1.469422375337606</v>
+        <v>1.53774099031928</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0.1151917576789856</v>
+        <v>0.1151440143585205</v>
       </c>
       <c r="JB73" t="n">
         <v>-0.3</v>
       </c>
       <c r="JC73" t="n">
-        <v>1.469421517404021</v>
+        <v>1.537740132385695</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0.126730352640152</v>
+        <v>0.1266944110393524</v>
       </c>
       <c r="JB74" t="n">
         <v>-0.3</v>
       </c>
       <c r="JC74" t="n">
-        <v>1.469421745725056</v>
+        <v>1.537740360706729</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0.1174194365739822</v>
+        <v>0.1173795610666275</v>
       </c>
       <c r="JB75" t="n">
         <v>-0.3</v>
       </c>
       <c r="JC75" t="n">
-        <v>1.469420950060844</v>
+        <v>1.537739565042518</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0.1121200770139694</v>
+        <v>0.1120632886886597</v>
       </c>
       <c r="JB76" t="n">
         <v>-0.16</v>
       </c>
       <c r="JC76" t="n">
-        <v>1.469421012330217</v>
+        <v>1.53773962731189</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0.113911509513855</v>
+        <v>0.1138574033975601</v>
       </c>
       <c r="JB77" t="n">
         <v>-0.16</v>
       </c>
       <c r="JC77" t="n">
-        <v>1.469421040005494</v>
+        <v>1.537739654987168</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0.1240866184234619</v>
+        <v>0.1240344941616058</v>
       </c>
       <c r="JB78" t="n">
         <v>-0.16</v>
       </c>
       <c r="JC78" t="n">
-        <v>1.469421192219517</v>
+        <v>1.53773980720119</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0.1127874702215195</v>
+        <v>0.1127274334430695</v>
       </c>
       <c r="JB79" t="n">
         <v>-0.16</v>
       </c>
       <c r="JC79" t="n">
-        <v>1.469420846278556</v>
+        <v>1.537739461260229</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0.1093562245368958</v>
+        <v>0.1092921644449234</v>
       </c>
       <c r="JB80" t="n">
         <v>0.5799999999999998</v>
       </c>
       <c r="JC80" t="n">
-        <v>1.469420922385567</v>
+        <v>1.53773953736724</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0.07885172963142395</v>
+        <v>0.07879526913166046</v>
       </c>
       <c r="JB81" t="n">
         <v>0.5799999999999998</v>
       </c>
       <c r="JC81" t="n">
-        <v>1.469421088437229</v>
+        <v>1.537739703418902</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0.1233917027711868</v>
+        <v>0.1233393847942352</v>
       </c>
       <c r="JB82" t="n">
         <v>0.7199999999999999</v>
       </c>
       <c r="JC82" t="n">
-        <v>1.469421448215829</v>
+        <v>1.537740063197502</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0.1286185681819916</v>
+        <v>0.1285761594772339</v>
       </c>
       <c r="JB83" t="n">
         <v>0.8599999999999999</v>
       </c>
       <c r="JC83" t="n">
-        <v>1.469421468972287</v>
+        <v>1.53774008395396</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0.1249295026063919</v>
+        <v>0.1248839795589447</v>
       </c>
       <c r="JB84" t="n">
         <v>0.7199999999999999</v>
       </c>
       <c r="JC84" t="n">
-        <v>1.469421572754575</v>
+        <v>1.537740187736248</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0.1109867841005325</v>
+        <v>0.1109272390604019</v>
       </c>
       <c r="JB85" t="n">
         <v>0.4399999999999999</v>
       </c>
       <c r="JC85" t="n">
-        <v>1.46942180107561</v>
+        <v>1.537740416057283</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0.08967211842536926</v>
+        <v>0.089609295129776</v>
       </c>
       <c r="JB86" t="n">
         <v>-0.3</v>
       </c>
       <c r="JC86" t="n">
-        <v>1.469421676536864</v>
+        <v>1.537740291518537</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0.05787215381860733</v>
+        <v>0.05781985074281693</v>
       </c>
       <c r="JB87" t="n">
         <v>-0.5799999999999998</v>
       </c>
       <c r="JC87" t="n">
-        <v>1.469421704212141</v>
+        <v>1.537740319193814</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0.1142780333757401</v>
+        <v>0.1142211854457855</v>
       </c>
       <c r="JB88" t="n">
         <v>-0.8599999999999999</v>
       </c>
       <c r="JC88" t="n">
-        <v>1.469421759562694</v>
+        <v>1.537740374544368</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0.1003818958997726</v>
+        <v>0.1003221273422241</v>
       </c>
       <c r="JB89" t="n">
         <v>-0.8599999999999999</v>
       </c>
       <c r="JC89" t="n">
-        <v>1.469422022477825</v>
+        <v>1.537740637459498</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0.09472367167472839</v>
+        <v>0.09466195106506348</v>
       </c>
       <c r="JB90" t="n">
         <v>-0.8599999999999999</v>
       </c>
       <c r="JC90" t="n">
-        <v>1.469421939451994</v>
+        <v>1.537740554433668</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0.07490748167037964</v>
+        <v>0.07484737038612366</v>
       </c>
       <c r="JB91" t="n">
         <v>-0.9999999999999998</v>
       </c>
       <c r="JC91" t="n">
-        <v>1.469421731887417</v>
+        <v>1.537740346869091</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0.06866241991519928</v>
+        <v>0.06860385835170746</v>
       </c>
       <c r="JB92" t="n">
         <v>-0.9999999999999998</v>
       </c>
       <c r="JC92" t="n">
-        <v>1.469421745725056</v>
+        <v>1.537740360706729</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0.07032811641693115</v>
+        <v>0.07026936113834381</v>
       </c>
       <c r="JB93" t="n">
         <v>-0.9999999999999998</v>
       </c>
       <c r="JC93" t="n">
-        <v>1.469421884101441</v>
+        <v>1.537740499083114</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0.06969055533409119</v>
+        <v>0.06963044404983521</v>
       </c>
       <c r="JB94" t="n">
         <v>-0.9999999999999998</v>
       </c>
       <c r="JC94" t="n">
-        <v>1.469421600429852</v>
+        <v>1.537740215411525</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0.05086024105548859</v>
+        <v>0.05080674588680267</v>
       </c>
       <c r="JB95" t="n">
         <v>-0.9999999999999998</v>
       </c>
       <c r="JC95" t="n">
-        <v>1.469421427459371</v>
+        <v>1.537740042441045</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0.09190917015075684</v>
+        <v>0.09184810519218445</v>
       </c>
       <c r="JB96" t="n">
         <v>-0.9999999999999998</v>
       </c>
       <c r="JC96" t="n">
-        <v>1.469421323677083</v>
+        <v>1.537739938658756</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0.07209713757038116</v>
+        <v>0.07203613221645355</v>
       </c>
       <c r="JB97" t="n">
         <v>-0.9999999999999998</v>
       </c>
       <c r="JC97" t="n">
-        <v>1.469421468972287</v>
+        <v>1.53774008395396</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0.05599900335073471</v>
+        <v>0.05594208836555481</v>
       </c>
       <c r="JB98" t="n">
         <v>-0.9999999999999998</v>
       </c>
       <c r="JC98" t="n">
-        <v>1.46942171113096</v>
+        <v>1.537740326112633</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0.07262274622917175</v>
+        <v>0.07256138324737549</v>
       </c>
       <c r="JB99" t="n">
         <v>-0.9999999999999998</v>
       </c>
       <c r="JC99" t="n">
-        <v>1.469421538160479</v>
+        <v>1.537740153142152</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0.04197688400745392</v>
+        <v>0.04192320257425308</v>
       </c>
       <c r="JB100" t="n">
         <v>-0.9999999999999998</v>
       </c>
       <c r="JC100" t="n">
-        <v>1.469421240651252</v>
+        <v>1.537739855632925</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0.07517622411251068</v>
+        <v>0.07511492073535919</v>
       </c>
       <c r="JB101" t="n">
         <v>-0.9999999999999998</v>
       </c>
       <c r="JC101" t="n">
-        <v>1.469421226813614</v>
+        <v>1.537739841795287</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0.04714910686016083</v>
+        <v>0.04709320515394211</v>
       </c>
       <c r="JB102" t="n">
         <v>-0.1199999999999999</v>
       </c>
       <c r="JC102" t="n">
-        <v>1.469420860116194</v>
+        <v>1.537739475097867</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0.06551635265350342</v>
+        <v>0.06546667218208313</v>
       </c>
       <c r="JB103" t="n">
         <v>-0.1199999999999999</v>
       </c>
       <c r="JC103" t="n">
-        <v>1.469420860116194</v>
+        <v>1.537739475097867</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0.1215920001268387</v>
+        <v>0.1215329617261887</v>
       </c>
       <c r="JB104" t="n">
         <v>-0.1199999999999999</v>
       </c>
       <c r="JC104" t="n">
-        <v>1.469420797846821</v>
+        <v>1.537739412828494</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0.065299391746521</v>
+        <v>0.06523871421813965</v>
       </c>
       <c r="JB105" t="n">
         <v>0.02000000000000007</v>
       </c>
       <c r="JC105" t="n">
-        <v>1.469420694064532</v>
+        <v>1.537739309046206</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0.05896015465259552</v>
+        <v>0.05890234559774399</v>
       </c>
       <c r="JB106" t="n">
         <v>0.02000000000000007</v>
       </c>
       <c r="JC106" t="n">
-        <v>1.469420521094052</v>
+        <v>1.537739136075725</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0.08447001874446869</v>
+        <v>0.08440673351287842</v>
       </c>
       <c r="JB107" t="n">
         <v>-0.2599999999999998</v>
       </c>
       <c r="JC107" t="n">
-        <v>1.469420569525786</v>
+        <v>1.53773918450746</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0.06497544050216675</v>
+        <v>0.06491252779960632</v>
       </c>
       <c r="JB108" t="n">
         <v>-0.1199999999999999</v>
       </c>
       <c r="JC108" t="n">
-        <v>1.469420209747186</v>
+        <v>1.53773882472886</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0.03285772353410721</v>
+        <v>0.03280588239431381</v>
       </c>
       <c r="JB109" t="n">
         <v>-0.7199999999999999</v>
       </c>
       <c r="JC109" t="n">
-        <v>1.469420168234271</v>
+        <v>1.537738783215944</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0.08184598386287689</v>
+        <v>0.08178184926509857</v>
       </c>
       <c r="JB110" t="n">
         <v>-0.8599999999999999</v>
       </c>
       <c r="JC110" t="n">
-        <v>1.469420223584825</v>
+        <v>1.537738838566498</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0.03089819848537445</v>
+        <v>0.03084325790405273</v>
       </c>
       <c r="JB111" t="n">
         <v>-0.8599999999999999</v>
       </c>
       <c r="JC111" t="n">
-        <v>1.469420278935379</v>
+        <v>1.537738893917052</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0.03772711753845215</v>
+        <v>0.03767073154449463</v>
       </c>
       <c r="JB112" t="n">
         <v>-0.8599999999999999</v>
       </c>
       <c r="JC112" t="n">
-        <v>1.469420320448294</v>
+        <v>1.537738935429968</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0.02560999244451523</v>
+        <v>0.02555616199970245</v>
       </c>
       <c r="JB113" t="n">
         <v>-0.9999999999999998</v>
       </c>
       <c r="JC113" t="n">
-        <v>1.469420050614344</v>
+        <v>1.537738665596017</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0.02638468891382217</v>
+        <v>0.02633166313171387</v>
       </c>
       <c r="JB114" t="n">
         <v>-0.9999999999999998</v>
       </c>
       <c r="JC114" t="n">
-        <v>1.469420105964898</v>
+        <v>1.537738720946571</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0.02851010113954544</v>
+        <v>0.02845628559589386</v>
       </c>
       <c r="JB115" t="n">
         <v>-0.9999999999999998</v>
       </c>
       <c r="JC115" t="n">
-        <v>1.469420251260102</v>
+        <v>1.537738866241775</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0.02760164439678192</v>
+        <v>0.02754767239093781</v>
       </c>
       <c r="JB116" t="n">
         <v>-0.7199999999999999</v>
       </c>
       <c r="JC116" t="n">
-        <v>1.469420216666006</v>
+        <v>1.537738831647679</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0.01872124522924423</v>
+        <v>0.01867594569921494</v>
       </c>
       <c r="JB117" t="n">
         <v>0.16</v>
       </c>
       <c r="JC117" t="n">
-        <v>1.469420202828367</v>
+        <v>1.53773881781004</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0.09850198030471802</v>
+        <v>0.09845355153083801</v>
       </c>
       <c r="JB118" t="n">
         <v>0.4399999999999999</v>
       </c>
       <c r="JC118" t="n">
-        <v>1.469420292773017</v>
+        <v>1.53773890775469</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0.1050640344619751</v>
+        <v>0.105038583278656</v>
       </c>
       <c r="JB119" t="n">
         <v>0.7199999999999999</v>
       </c>
       <c r="JC119" t="n">
-        <v>1.469420611038702</v>
+        <v>1.537739226020375</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0.1240935325622559</v>
+        <v>0.124036893248558</v>
       </c>
       <c r="JB120" t="n">
         <v>0.9999999999999998</v>
       </c>
       <c r="JC120" t="n">
-        <v>1.469420431149402</v>
+        <v>1.537739046131075</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0.1077306270599365</v>
+        <v>0.1076663881540298</v>
       </c>
       <c r="JB121" t="n">
         <v>0.8599999999999999</v>
       </c>
       <c r="JC121" t="n">
-        <v>1.469420472662317</v>
+        <v>1.53773908764399</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0.09270629286766052</v>
+        <v>0.09264053404331207</v>
       </c>
       <c r="JB122" t="n">
         <v>0.7199999999999999</v>
       </c>
       <c r="JC122" t="n">
-        <v>1.469420285854198</v>
+        <v>1.537738900835871</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0.06164383888244629</v>
+        <v>0.06158418208360672</v>
       </c>
       <c r="JB123" t="n">
         <v>0.4399999999999999</v>
       </c>
       <c r="JC123" t="n">
-        <v>1.46942035504239</v>
+        <v>1.537738970024063</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0.08111986517906189</v>
+        <v>0.08105514943599701</v>
       </c>
       <c r="JB124" t="n">
         <v>0.3</v>
       </c>
       <c r="JC124" t="n">
-        <v>1.469420154396633</v>
+        <v>1.537738769378306</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0.04323892295360565</v>
+        <v>0.04318273067474365</v>
       </c>
       <c r="JB125" t="n">
         <v>-0.5100000000000003</v>
       </c>
       <c r="JC125" t="n">
-        <v>1.469420195909548</v>
+        <v>1.537738810891221</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0.0832417905330658</v>
+        <v>0.08318743109703064</v>
       </c>
       <c r="JB126" t="n">
         <v>-0.7200000000000004</v>
       </c>
       <c r="JC126" t="n">
-        <v>1.469420223584825</v>
+        <v>1.537738838566498</v>
       </c>
     </row>
   </sheetData>
